--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325456</v>
+        <v>127325591</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566433</v>
+        <v>566560</v>
       </c>
       <c r="R3" t="n">
-        <v>6990739</v>
+        <v>6990765</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -976,50 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325591</v>
+        <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566560</v>
+        <v>566433</v>
       </c>
       <c r="R5" t="n">
-        <v>6990765</v>
+        <v>6990739</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1052,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -879,50 +879,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325494</v>
+        <v>127325456</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566528</v>
+        <v>566433</v>
       </c>
       <c r="R4" t="n">
-        <v>6990696</v>
+        <v>6990739</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -955,11 +950,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,45 +976,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325456</v>
+        <v>127325494</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566433</v>
+        <v>566528</v>
       </c>
       <c r="R5" t="n">
-        <v>6990739</v>
+        <v>6990696</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -879,45 +879,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325456</v>
+        <v>127325494</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566433</v>
+        <v>566528</v>
       </c>
       <c r="R4" t="n">
-        <v>6990739</v>
+        <v>6990696</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -950,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,50 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325494</v>
+        <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566528</v>
+        <v>566433</v>
       </c>
       <c r="R5" t="n">
-        <v>6990696</v>
+        <v>6990739</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1052,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325619</v>
       </c>
       <c r="B2" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325591</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127325494</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127325585</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127325534</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127325482</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>127325473</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325591</v>
+        <v>127325494</v>
       </c>
       <c r="B3" t="n">
         <v>57661</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566560</v>
+        <v>566528</v>
       </c>
       <c r="R3" t="n">
-        <v>6990765</v>
+        <v>6990696</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325494</v>
+        <v>127325591</v>
       </c>
       <c r="B4" t="n">
         <v>57661</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566528</v>
+        <v>566560</v>
       </c>
       <c r="R4" t="n">
-        <v>6990696</v>
+        <v>6990765</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325619</v>
       </c>
       <c r="B2" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325494</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127325591</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127325585</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127325534</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127325482</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>127325473</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325494</v>
+        <v>127325591</v>
       </c>
       <c r="B3" t="n">
         <v>57663</v>
@@ -812,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566528</v>
+        <v>566560</v>
       </c>
       <c r="R3" t="n">
-        <v>6990696</v>
+        <v>6990765</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325591</v>
+        <v>127325494</v>
       </c>
       <c r="B4" t="n">
         <v>57663</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566560</v>
+        <v>566528</v>
       </c>
       <c r="R4" t="n">
-        <v>6990765</v>
+        <v>6990696</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325591</v>
+        <v>127325456</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566560</v>
+        <v>566433</v>
       </c>
       <c r="R3" t="n">
-        <v>6990765</v>
+        <v>6990739</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325494</v>
+        <v>127325591</v>
       </c>
       <c r="B4" t="n">
         <v>57663</v>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566528</v>
+        <v>566560</v>
       </c>
       <c r="R4" t="n">
-        <v>6990696</v>
+        <v>6990765</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,45 +976,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325456</v>
+        <v>127325494</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566433</v>
+        <v>566528</v>
       </c>
       <c r="R5" t="n">
-        <v>6990739</v>
+        <v>6990696</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325456</v>
+        <v>127325494</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566433</v>
+        <v>566528</v>
       </c>
       <c r="R3" t="n">
-        <v>6990739</v>
+        <v>6990696</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -976,50 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325494</v>
+        <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566528</v>
+        <v>566433</v>
       </c>
       <c r="R5" t="n">
-        <v>6990696</v>
+        <v>6990739</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1052,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325619</v>
       </c>
       <c r="B2" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325494</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127325591</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127325585</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127325534</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127325482</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>127325473</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325619</v>
       </c>
       <c r="B2" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325494</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>127325591</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>127325585</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>127325534</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>127325482</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>127325473</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,50 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325494</v>
+        <v>127325456</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566528</v>
+        <v>566433</v>
       </c>
       <c r="R3" t="n">
-        <v>6990696</v>
+        <v>6990739</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -848,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325591</v>
+        <v>127325494</v>
       </c>
       <c r="B4" t="n">
         <v>57672</v>
@@ -919,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566560</v>
+        <v>566528</v>
       </c>
       <c r="R4" t="n">
-        <v>6990765</v>
+        <v>6990696</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -959,7 +949,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,45 +976,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325456</v>
+        <v>127325591</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566433</v>
+        <v>566560</v>
       </c>
       <c r="R5" t="n">
-        <v>6990739</v>
+        <v>6990765</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1057,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 22190-2025 artfynd.xlsx
+++ b/artfynd/A 22190-2025 artfynd.xlsx
@@ -772,45 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325456</v>
+        <v>127325494</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566433</v>
+        <v>566528</v>
       </c>
       <c r="R3" t="n">
-        <v>6990739</v>
+        <v>6990696</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,6 +848,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325494</v>
+        <v>127325591</v>
       </c>
       <c r="B4" t="n">
         <v>57672</v>
@@ -909,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566528</v>
+        <v>566560</v>
       </c>
       <c r="R4" t="n">
-        <v>6990696</v>
+        <v>6990765</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -949,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack på gran</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,50 +986,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325591</v>
+        <v>127325456</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bebgtsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566560</v>
+        <v>566433</v>
       </c>
       <c r="R5" t="n">
-        <v>6990765</v>
+        <v>6990739</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1052,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
